--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1292,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1311,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1374,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1389,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1438,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1452,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44680</v>
+        <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1468,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1511,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1525,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45673</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1541,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1584,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,14 +1594,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45527</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1614,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1657,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1652,14 +1667,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44489</v>
+        <v>45838</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1687,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45146</v>
+        <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1760,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1817,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45922</v>
+        <v>45798</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1861,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1890,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45798</v>
+        <v>45169</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1906,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46092</v>
+        <v>45594</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46099</v>
+        <v>45673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44769</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45055</v>
+        <v>46099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45673</v>
+        <v>46112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44838</v>
+        <v>46135</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45587</v>
+        <v>45406</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2535,7 +2550,7 @@
         <v>46136</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2591,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45637</v>
+        <v>45810</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2694,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45810</v>
+        <v>45222</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2767,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2810,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45737</v>
+        <v>46149</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2839,13 +2854,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44907</v>
+        <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>45642</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46038</v>
+        <v>46128</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46037</v>
+        <v>46160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45406</v>
+        <v>46176</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45594</v>
+        <v>46185</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3336,14 +3346,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45640</v>
+        <v>46195</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45026</v>
+        <v>46238</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46149</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45372</v>
+        <v>46203</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46160</v>
+        <v>46248</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>46248</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>45055</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46176</v>
+        <v>46266</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45724</v>
+        <v>45446</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45169</v>
+        <v>45594</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46185</v>
+        <v>44680</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46238</v>
+        <v>45026</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46195</v>
+        <v>45616</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>45673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45222</v>
+        <v>45372</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46203</v>
+        <v>44907</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46248</v>
+        <v>44769</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46248</v>
+        <v>45587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45616</v>
+        <v>45146</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46266</v>
+        <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45594</v>
+        <v>45637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4876,7 +4886,7 @@
         <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4932,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4946,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45085</v>
+        <v>45724</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4962,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5015,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5034,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5083,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5093,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45803</v>
+        <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5112,13 +5117,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>45208</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45803</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,13 +1233,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>45798</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1311,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1360,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1374,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45737</v>
+        <v>45724</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1389,13 +1379,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1438,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1452,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46037</v>
+        <v>45169</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1468,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1511,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46038</v>
+        <v>44862</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1541,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1584,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1598,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1614,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1657,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1667,14 +1652,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45838</v>
+        <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1687,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1744,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45922</v>
+        <v>46092</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1760,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1803,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1817,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45798</v>
+        <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45169</v>
+        <v>46112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45594</v>
+        <v>45428</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45673</v>
+        <v>45922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44680</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46092</v>
+        <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46099</v>
+        <v>46135</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46112</v>
+        <v>45810</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46135</v>
+        <v>44489</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45406</v>
+        <v>46136</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46136</v>
+        <v>45146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45810</v>
+        <v>45406</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46136</v>
+        <v>45222</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2694,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45222</v>
+        <v>44769</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2767,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2842,7 +2827,7 @@
         <v>46149</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2898,7 +2883,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2897,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44838</v>
+        <v>46160</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2913,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2956,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2970,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>45737</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3000,8 +2985,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46128</v>
+        <v>45642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46160</v>
+        <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46176</v>
+        <v>46128</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46185</v>
+        <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46195</v>
+        <v>44838</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46238</v>
+        <v>46038</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>46037</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46203</v>
+        <v>45587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46248</v>
+        <v>45637</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46248</v>
+        <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45055</v>
+        <v>44907</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46266</v>
+        <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45446</v>
+        <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4010,7 +4000,7 @@
         <v>45594</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4066,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4076,14 +4066,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44680</v>
+        <v>45640</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4156,7 +4146,7 @@
         <v>45026</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4219,7 @@
         <v>45616</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4285,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45673</v>
+        <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45372</v>
+        <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44907</v>
+        <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44769</v>
+        <v>45372</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45587</v>
+        <v>45594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45146</v>
+        <v>46266</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45085</v>
+        <v>45712</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45637</v>
+        <v>45085</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>7.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4873,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>46238</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4889,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4932,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4942,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45724</v>
+        <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4971,8 +4961,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5020,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5044,8 +5039,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44489</v>
+        <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45208</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1292,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45798</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1311,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1374,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45724</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1390,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1433,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1447,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45169</v>
+        <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1463,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1506,14 +1516,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44862</v>
+        <v>45838</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1593,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45673</v>
+        <v>45922</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1609,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1666,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45527</v>
+        <v>46038</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1725,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1739,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46092</v>
+        <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1755,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1812,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46099</v>
+        <v>45594</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46112</v>
+        <v>45798</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1958,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45428</v>
+        <v>45208</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1974,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45922</v>
+        <v>45673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44680</v>
+        <v>46092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46136</v>
+        <v>45737</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2182,8 +2192,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46135</v>
+        <v>45222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45810</v>
+        <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44489</v>
+        <v>44838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46136</v>
+        <v>46112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45146</v>
+        <v>45428</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45406</v>
+        <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45222</v>
+        <v>45406</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2694,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44769</v>
+        <v>45055</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2767,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2810,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2840,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2883,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2897,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46160</v>
+        <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2913,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2956,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2970,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45737</v>
+        <v>45446</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2985,13 +3000,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45642</v>
+        <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45055</v>
+        <v>45594</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46128</v>
+        <v>44680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45673</v>
+        <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44838</v>
+        <v>45026</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46038</v>
+        <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46037</v>
+        <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45587</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45637</v>
+        <v>46160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46176</v>
+        <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44907</v>
+        <v>46176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46185</v>
+        <v>45372</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46195</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45594</v>
+        <v>44907</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4066,14 +4076,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45640</v>
+        <v>44769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45026</v>
+        <v>46195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45616</v>
+        <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4365,7 +4375,7 @@
         <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46248</v>
+        <v>45587</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45372</v>
+        <v>45146</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45594</v>
+        <v>45085</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4657,7 +4667,7 @@
         <v>46266</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45712</v>
+        <v>45637</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45085</v>
+        <v>45712</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46238</v>
+        <v>45724</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4889,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4932,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4942,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4961,13 +4971,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5010,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5020,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5039,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>46238</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45803</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,13 +1233,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1311,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1377,7 +1367,7 @@
         <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1433,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46037</v>
+        <v>44680</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1516,14 +1506,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1589,14 +1579,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45922</v>
+        <v>45838</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1666,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46038</v>
+        <v>46092</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1725,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1739,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45169</v>
+        <v>44489</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1755,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45594</v>
+        <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1828,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1885,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45798</v>
+        <v>45146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1901,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1944,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1958,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45208</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1974,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45673</v>
+        <v>45798</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46092</v>
+        <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45737</v>
+        <v>44769</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2192,13 +2182,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45222</v>
+        <v>46135</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46099</v>
+        <v>45810</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44838</v>
+        <v>45922</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46112</v>
+        <v>46136</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45428</v>
+        <v>45055</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46135</v>
+        <v>45406</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45406</v>
+        <v>45673</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2694,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45055</v>
+        <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2767,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2810,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2824,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46136</v>
+        <v>45587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2840,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2883,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2897,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45810</v>
+        <v>45637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2913,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2956,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2970,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45446</v>
+        <v>46149</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +2986,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3029,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3043,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46136</v>
+        <v>44907</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3059,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3102,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3116,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45594</v>
+        <v>46160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3132,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3175,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3189,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44680</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3205,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3248,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3262,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46149</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3278,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3321,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3335,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45026</v>
+        <v>45594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3351,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3394,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3419,14 +3404,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45616</v>
+        <v>45640</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3424,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3467,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3481,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45642</v>
+        <v>45026</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3497,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3540,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3554,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3570,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3613,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3627,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3701,7 +3686,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3700,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45673</v>
+        <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3716,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3759,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3773,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46176</v>
+        <v>45372</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3789,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3832,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3846,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45372</v>
+        <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3862,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3905,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3919,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46185</v>
+        <v>46248</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3935,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3978,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +3992,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44907</v>
+        <v>46248</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4008,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4051,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4065,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44769</v>
+        <v>45724</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4081,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4124,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4138,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46195</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4154,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4197,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4211,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46203</v>
+        <v>46266</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4227,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4270,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4284,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46248</v>
+        <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4300,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4343,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4357,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46248</v>
+        <v>45737</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4387,8 +4372,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45587</v>
+        <v>45222</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.9</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45146</v>
+        <v>46238</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45085</v>
+        <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46266</v>
+        <v>46037</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45637</v>
+        <v>45616</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45712</v>
+        <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4873,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45724</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4889,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4932,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4946,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44862</v>
+        <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4962,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5005,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5015,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44489</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5044,8 +5034,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5083,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5093,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46238</v>
+        <v>45803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5117,8 +5112,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44680</v>
+        <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45673</v>
+        <v>45406</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46092</v>
+        <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44489</v>
+        <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46099</v>
+        <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45146</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45798</v>
+        <v>44838</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44769</v>
+        <v>45428</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46135</v>
+        <v>45055</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45810</v>
+        <v>45446</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45922</v>
+        <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46136</v>
+        <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45055</v>
+        <v>46160</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45406</v>
+        <v>45594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45673</v>
+        <v>44680</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44838</v>
+        <v>45026</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45587</v>
+        <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2883,7 +2883,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45637</v>
+        <v>45737</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2912,8 +2912,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2956,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2970,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46149</v>
+        <v>46037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2986,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44907</v>
+        <v>46038</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3059,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3102,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46160</v>
+        <v>45673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3132,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3175,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>46176</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3205,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3248,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3262,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>45372</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3278,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3321,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3335,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45594</v>
+        <v>46185</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3351,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3394,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3404,14 +3409,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45640</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3424,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3467,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3481,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45026</v>
+        <v>46092</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3497,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3540,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3554,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46176</v>
+        <v>44769</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3570,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3613,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3627,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46185</v>
+        <v>46099</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3643,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3703,7 +3708,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45372</v>
+        <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3789,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3832,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3846,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46203</v>
+        <v>46135</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3862,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3905,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3919,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46248</v>
+        <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3935,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3978,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3992,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46248</v>
+        <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4008,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4051,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45724</v>
+        <v>46248</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4124,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4138,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45169</v>
+        <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4197,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4211,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46266</v>
+        <v>46248</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4227,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4270,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4284,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4343,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4357,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45737</v>
+        <v>45637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4372,13 +4377,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45222</v>
+        <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46238</v>
+        <v>45724</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46038</v>
+        <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46037</v>
+        <v>46266</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45616</v>
+        <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45594</v>
+        <v>46238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4888,8 +4888,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4932,7 +4937,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4942,14 +4947,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45085</v>
+        <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4961,8 +4966,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5015,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5034,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5083,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5093,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45803</v>
+        <v>45798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5112,13 +5117,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45406</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>44838</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>46149</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45428</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45055</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45446</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>46160</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>44680</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45026</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45616</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45737</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46037</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46038</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>46176</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45372</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46185</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>46092</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>44769</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>46099</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>46135</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>46248</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>46248</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45724</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46266</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45838</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45169</v>
+        <v>45594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45594</v>
+        <v>45169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45406</v>
+        <v>46135</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45673</v>
+        <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46136</v>
+        <v>45673</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45810</v>
+        <v>45406</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1805,7 +1805,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45222</v>
+        <v>45810</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45922</v>
+        <v>46136</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44838</v>
+        <v>45922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>46149</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45428</v>
+        <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45055</v>
+        <v>45642</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45446</v>
+        <v>46128</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45642</v>
+        <v>46160</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46128</v>
+        <v>44838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46160</v>
+        <v>45428</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45594</v>
+        <v>46176</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44680</v>
+        <v>45055</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45026</v>
+        <v>45737</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2766,8 +2766,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2810,7 +2815,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2829,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45616</v>
+        <v>45446</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2840,7 +2845,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2883,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2897,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45737</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2912,13 +2917,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46038</v>
+        <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45673</v>
+        <v>45594</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46176</v>
+        <v>46195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.300000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45372</v>
+        <v>44680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46185</v>
+        <v>45026</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44907</v>
+        <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>46092</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44769</v>
+        <v>46099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46099</v>
+        <v>46203</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46195</v>
+        <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46135</v>
+        <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46203</v>
+        <v>46248</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45587</v>
+        <v>45372</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46248</v>
+        <v>44907</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45146</v>
+        <v>44769</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46248</v>
+        <v>46266</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45085</v>
+        <v>45587</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45637</v>
+        <v>45146</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45712</v>
+        <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45724</v>
+        <v>45085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44862</v>
+        <v>45637</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46266</v>
+        <v>45712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44489</v>
+        <v>45724</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46238</v>
+        <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45803</v>
+        <v>44489</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4888,13 +4888,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4937,7 +4932,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4954,7 +4949,7 @@
         <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4967,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5020,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45838</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5044,8 +5039,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45798</v>
+        <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>44769</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45208</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45594</v>
+        <v>45055</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45169</v>
+        <v>45673</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45208</v>
+        <v>44838</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46135</v>
+        <v>45587</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45798</v>
+        <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>45673</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45406</v>
+        <v>45637</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46136</v>
+        <v>44862</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45810</v>
+        <v>44907</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46136</v>
+        <v>45527</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45922</v>
+        <v>45594</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2090,14 +2090,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46149</v>
+        <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2109,8 +2109,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2158,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2172,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45222</v>
+        <v>45922</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2188,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2231,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2236,14 +2241,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45642</v>
+        <v>45803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2255,8 +2260,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2309,14 +2319,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46128</v>
+        <v>45640</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46160</v>
+        <v>45026</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44838</v>
+        <v>44680</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45428</v>
+        <v>45372</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46176</v>
+        <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2631,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45055</v>
+        <v>45146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2694,7 +2704,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2747,14 +2757,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45737</v>
+        <v>45838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2766,13 +2776,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2815,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2829,10 +2834,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45446</v>
+        <v>45724</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2845,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46038</v>
+        <v>45169</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +2996,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3039,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3053,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46185</v>
+        <v>46037</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45594</v>
+        <v>45737</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3136,8 +3141,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46195</v>
+        <v>46238</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44680</v>
+        <v>45428</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45026</v>
+        <v>45222</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45616</v>
+        <v>46092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46203</v>
+        <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45673</v>
+        <v>45616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46112</v>
+        <v>46135</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46248</v>
+        <v>45798</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46248</v>
+        <v>45810</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>2.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45372</v>
+        <v>46136</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44907</v>
+        <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44769</v>
+        <v>45406</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46266</v>
+        <v>45712</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45587</v>
+        <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45146</v>
+        <v>46149</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46238</v>
+        <v>46160</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45085</v>
+        <v>45642</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.4</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45637</v>
+        <v>46128</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45712</v>
+        <v>46176</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45724</v>
+        <v>46185</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44862</v>
+        <v>46195</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44489</v>
+        <v>46203</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4889,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4932,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4942,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45803</v>
+        <v>46248</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4961,13 +4971,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5010,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5020,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5039,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 44601-2022</t>
+          <t>A 37214-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44840</v>
+        <v>44806</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37214-2022</t>
+          <t>A 44601-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44806</v>
+        <v>44840</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44769</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44811</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45208</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45055</v>
+        <v>45594</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45673</v>
+        <v>45169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44838</v>
+        <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45587</v>
+        <v>46135</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45446</v>
+        <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>45673</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45637</v>
+        <v>45406</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44862</v>
+        <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44907</v>
+        <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45527</v>
+        <v>45810</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45594</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2090,14 +2090,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45803</v>
+        <v>46136</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2109,13 +2109,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2158,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45922</v>
+        <v>44838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2188,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2231,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2241,14 +2236,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45803</v>
+        <v>45428</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2260,13 +2255,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2319,14 +2309,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45640</v>
+        <v>46149</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45026</v>
+        <v>45055</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44680</v>
+        <v>45642</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45372</v>
+        <v>46128</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44489</v>
+        <v>46160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2631,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45146</v>
+        <v>45737</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2703,8 +2693,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2742,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2757,14 +2752,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45838</v>
+        <v>45446</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2777,7 +2772,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2820,7 +2815,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2834,10 +2829,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45724</v>
+        <v>45594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2845,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2918,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45169</v>
+        <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2996,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3039,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3053,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46037</v>
+        <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3069,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45737</v>
+        <v>45026</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3141,13 +3136,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46238</v>
+        <v>45616</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45428</v>
+        <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45222</v>
+        <v>46092</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46092</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3499,7 +3489,7 @@
         <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3555,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46112</v>
+        <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46136</v>
+        <v>46112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45616</v>
+        <v>45372</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46135</v>
+        <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45798</v>
+        <v>44907</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45810</v>
+        <v>44769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46136</v>
+        <v>46203</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45594</v>
+        <v>46248</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45406</v>
+        <v>46248</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4159,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45712</v>
+        <v>45587</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45085</v>
+        <v>45146</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46149</v>
+        <v>46266</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46160</v>
+        <v>45085</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45642</v>
+        <v>45637</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46128</v>
+        <v>45712</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46176</v>
+        <v>45724</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46185</v>
+        <v>46238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46195</v>
+        <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4873,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46203</v>
+        <v>44489</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4889,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4932,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4942,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46248</v>
+        <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4971,8 +4961,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5010,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5020,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46248</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5044,8 +5039,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46266</v>
+        <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 37214-2022</t>
+          <t>A 44601-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>44806</v>
+        <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 44601-2022</t>
+          <t>A 37214-2022</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44840</v>
+        <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45594</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45169</v>
+        <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1379,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1428,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45208</v>
+        <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1458,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1501,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1515,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46135</v>
+        <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1531,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1574,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1588,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45798</v>
+        <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1604,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1647,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1661,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45673</v>
+        <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1677,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1720,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1725,14 +1730,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45406</v>
+        <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1744,8 +1749,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1812,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46136</v>
+        <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1871,14 +1881,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45922</v>
+        <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1890,8 +1900,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45810</v>
+        <v>44680</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45222</v>
+        <v>46092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46136</v>
+        <v>46099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44838</v>
+        <v>44489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45428</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46149</v>
+        <v>45146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45055</v>
+        <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45642</v>
+        <v>46135</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46128</v>
+        <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46160</v>
+        <v>44769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45737</v>
+        <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2693,13 +2708,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2742,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2756,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45446</v>
+        <v>45406</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2772,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2815,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2829,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45594</v>
+        <v>45055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2845,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46038</v>
+        <v>44838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44680</v>
+        <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45026</v>
+        <v>46149</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45616</v>
+        <v>45637</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3263,14 +3273,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46176</v>
+        <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46092</v>
+        <v>46160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45673</v>
+        <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46099</v>
+        <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46185</v>
+        <v>44907</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46112</v>
+        <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45372</v>
+        <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3774,14 +3784,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46195</v>
+        <v>45640</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44907</v>
+        <v>45026</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44769</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46203</v>
+        <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46248</v>
+        <v>46203</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46248</v>
+        <v>45798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45587</v>
+        <v>45372</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45146</v>
+        <v>46266</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46266</v>
+        <v>45724</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45085</v>
+        <v>45169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45637</v>
+        <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45712</v>
+        <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45724</v>
+        <v>45222</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44862</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44489</v>
+        <v>45616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4889,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4932,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4942,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45803</v>
+        <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4961,13 +4971,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5010,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5020,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5039,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>45085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44680</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>46092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46135</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>44769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45406</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46149</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45637</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44907</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45640</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45026</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46203</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45372</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>46266</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45724</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45222</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>46038</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>46037</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45803</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44680</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>46092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>46135</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>44769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45406</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46149</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45637</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45838</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46160</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44907</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45640</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45026</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46203</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45798</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45372</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>46266</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45724</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45222</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1292,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1311,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1374,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45737</v>
+        <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,13 +1389,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1445,7 +1450,7 @@
         <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1501,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1515,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45673</v>
+        <v>45737</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1528,6 +1533,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>GRÄSTORP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1574,7 +1584,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1584,14 +1594,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46038</v>
+        <v>45838</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1604,7 +1614,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1647,7 +1657,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1661,10 +1671,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46037</v>
+        <v>45169</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1677,7 +1687,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1720,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1730,14 +1740,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45803</v>
+        <v>45594</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1749,13 +1759,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45922</v>
+        <v>45798</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1871,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,14 +1886,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45803</v>
+        <v>46037</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1900,13 +1905,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44680</v>
+        <v>45673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46092</v>
+        <v>46038</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46099</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44489</v>
+        <v>46092</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45146</v>
+        <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46136</v>
+        <v>46112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46135</v>
+        <v>44838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45810</v>
+        <v>45428</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44769</v>
+        <v>46135</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46136</v>
+        <v>45406</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45406</v>
+        <v>46136</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2842,7 +2842,7 @@
         <v>45055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45673</v>
+        <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44838</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45587</v>
+        <v>45446</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46149</v>
+        <v>45594</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45637</v>
+        <v>44680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45838</v>
+        <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46160</v>
+        <v>45026</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45642</v>
+        <v>45616</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46128</v>
+        <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44907</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45594</v>
+        <v>46160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46176</v>
+        <v>45673</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45640</v>
+        <v>46176</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45026</v>
+        <v>45372</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46195</v>
+        <v>44907</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46203</v>
+        <v>44769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45798</v>
+        <v>46195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45372</v>
+        <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46266</v>
+        <v>45587</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>5.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45724</v>
+        <v>45146</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45169</v>
+        <v>46266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45428</v>
+        <v>45085</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46238</v>
+        <v>45637</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45222</v>
+        <v>45712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46248</v>
+        <v>45724</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46248</v>
+        <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45616</v>
+        <v>44489</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45594</v>
+        <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45712</v>
+        <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45085</v>
+        <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45803</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,13 +1233,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1311,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1360,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1374,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45922</v>
+        <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1389,8 +1379,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1433,7 +1428,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,10 +1442,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1458,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1501,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1515,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45737</v>
+        <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1535,13 +1530,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1584,7 +1574,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1594,14 +1584,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1613,8 +1603,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1657,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1667,14 +1662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45169</v>
+        <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1686,8 +1681,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45594</v>
+        <v>46038</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45798</v>
+        <v>46037</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46037</v>
+        <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1959,14 +1959,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46038</v>
+        <v>44680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>44489</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46092</v>
+        <v>45798</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45222</v>
+        <v>45146</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46099</v>
+        <v>44769</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44838</v>
+        <v>46099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45428</v>
+        <v>45055</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46135</v>
+        <v>45673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45406</v>
+        <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46136</v>
+        <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45055</v>
+        <v>45587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45810</v>
+        <v>45637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45446</v>
+        <v>44907</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45594</v>
+        <v>46135</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44680</v>
+        <v>45810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45026</v>
+        <v>45594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45616</v>
+        <v>45406</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3492,14 +3492,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45642</v>
+        <v>45640</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46128</v>
+        <v>45026</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46160</v>
+        <v>46149</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45673</v>
+        <v>45372</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46176</v>
+        <v>46160</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45372</v>
+        <v>45642</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46185</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44907</v>
+        <v>46176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44769</v>
+        <v>45724</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46195</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46203</v>
+        <v>46185</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45587</v>
+        <v>46195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45146</v>
+        <v>45428</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46266</v>
+        <v>46203</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45085</v>
+        <v>45222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45637</v>
+        <v>46266</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45712</v>
+        <v>45616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45724</v>
+        <v>45594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44862</v>
+        <v>46238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44489</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46238</v>
+        <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45169</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45594</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>44680</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45737</v>
+        <v>45026</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,13 +1379,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1428,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1442,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45673</v>
+        <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1501,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1515,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45527</v>
+        <v>45616</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1531,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1574,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1584,14 +1579,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45803</v>
+        <v>45085</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1603,13 +1598,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1662,14 +1652,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45803</v>
+        <v>45637</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1681,13 +1671,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1740,14 +1725,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46038</v>
+        <v>45640</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1760,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1803,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1817,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46037</v>
+        <v>45712</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45922</v>
+        <v>45673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1959,14 +1944,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45838</v>
+        <v>45724</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2022,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44680</v>
+        <v>44862</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2112,7 +2097,7 @@
         <v>44489</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2168,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45798</v>
+        <v>45372</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45146</v>
+        <v>45222</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44769</v>
+        <v>44907</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>44769</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46099</v>
+        <v>44838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2543,14 +2528,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45055</v>
+        <v>45803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2562,8 +2547,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2596,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2616,14 +2606,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45673</v>
+        <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2635,8 +2625,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46112</v>
+        <v>45428</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2704,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44838</v>
+        <v>45527</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2777,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2834,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45587</v>
+        <v>45055</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2908,14 +2903,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45637</v>
+        <v>45838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>45587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +2996,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3039,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44907</v>
+        <v>45146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46135</v>
+        <v>45446</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3142,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3185,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45810</v>
+        <v>45594</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3215,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3258,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3272,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46136</v>
+        <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3288,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3331,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45594</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3361,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3404,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3418,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45406</v>
+        <v>45922</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3434,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3477,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3492,14 +3487,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45640</v>
+        <v>45737</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3511,8 +3506,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45026</v>
+        <v>46037</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46149</v>
+        <v>46038</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45372</v>
+        <v>46092</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46160</v>
+        <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45642</v>
+        <v>46112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46176</v>
+        <v>45406</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45724</v>
+        <v>46136</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45169</v>
+        <v>45810</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46185</v>
+        <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46195</v>
+        <v>46149</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45428</v>
+        <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46203</v>
+        <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45222</v>
+        <v>46160</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46266</v>
+        <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45616</v>
+        <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45594</v>
+        <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46238</v>
+        <v>46203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>46266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45085</v>
+        <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45169</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45594</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44680</v>
+        <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1306,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1369,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45026</v>
+        <v>44862</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1385,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1428,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45208</v>
+        <v>45673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1496,7 +1501,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1515,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45616</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1531,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1574,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1588,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45085</v>
+        <v>46037</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1604,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1647,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1661,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45637</v>
+        <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1677,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1720,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1725,14 +1730,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45640</v>
+        <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1750,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1793,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1798,14 +1803,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45712</v>
+        <v>45803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1817,8 +1822,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1871,14 +1881,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45673</v>
+        <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1890,8 +1900,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45724</v>
+        <v>44680</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44862</v>
+        <v>46092</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44489</v>
+        <v>46099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45372</v>
+        <v>46112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45222</v>
+        <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44907</v>
+        <v>45146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44769</v>
+        <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44838</v>
+        <v>46135</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2528,14 +2543,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45803</v>
+        <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2547,13 +2562,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2596,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2606,14 +2616,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45803</v>
+        <v>44769</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2625,13 +2635,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45428</v>
+        <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2704,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45527</v>
+        <v>45406</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2777,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2820,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2830,14 +2835,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45055</v>
+        <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2903,14 +2908,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45838</v>
+        <v>45055</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45587</v>
+        <v>45673</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2996,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3039,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45146</v>
+        <v>44838</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3069,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45446</v>
+        <v>45798</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3142,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3185,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45594</v>
+        <v>45587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3215,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3258,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3272,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45798</v>
+        <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3288,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3331,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45637</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3404,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3418,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45922</v>
+        <v>44907</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3434,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3477,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3491,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45737</v>
+        <v>46160</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3506,13 +3511,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46037</v>
+        <v>45642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46038</v>
+        <v>46128</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46092</v>
+        <v>45594</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46099</v>
+        <v>45640</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46112</v>
+        <v>45026</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46135</v>
+        <v>46176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45406</v>
+        <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46136</v>
+        <v>45372</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45810</v>
+        <v>46195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46136</v>
+        <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46149</v>
+        <v>45724</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45642</v>
+        <v>45169</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46128</v>
+        <v>46266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46160</v>
+        <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46176</v>
+        <v>45222</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46185</v>
+        <v>46238</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46195</v>
+        <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46203</v>
+        <v>45616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46266</v>
+        <v>46248</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46238</v>
+        <v>45594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46248</v>
+        <v>45712</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46248</v>
+        <v>45085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45737</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1296,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45737</v>
+        <v>46037</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,13 +1311,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44862</v>
+        <v>46038</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45673</v>
+        <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1457,8 +1457,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1501,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1515,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46038</v>
+        <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1531,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1574,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1584,14 +1589,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46037</v>
+        <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1603,8 +1608,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1647,7 +1657,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1661,10 +1671,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45527</v>
+        <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1677,7 +1687,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1720,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1734,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45922</v>
+        <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1750,7 +1760,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1793,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1803,14 +1813,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45803</v>
+        <v>45594</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1822,13 +1832,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,14 +1886,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45803</v>
+        <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1900,13 +1905,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44680</v>
+        <v>45208</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46099</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46112</v>
+        <v>46135</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44489</v>
+        <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45146</v>
+        <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,7 +2404,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46135</v>
+        <v>45222</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2550,7 +2550,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44769</v>
+        <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46136</v>
+        <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45406</v>
+        <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2835,14 +2835,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45838</v>
+        <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45055</v>
+        <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45673</v>
+        <v>46128</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44838</v>
+        <v>46160</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45798</v>
+        <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45587</v>
+        <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46149</v>
+        <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45637</v>
+        <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44907</v>
+        <v>45594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46160</v>
+        <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45642</v>
+        <v>44680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46128</v>
+        <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45594</v>
+        <v>45026</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45640</v>
+        <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45026</v>
+        <v>45616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46176</v>
+        <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46185</v>
+        <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45372</v>
+        <v>46266</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46195</v>
+        <v>45372</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46203</v>
+        <v>46238</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45724</v>
+        <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45169</v>
+        <v>44769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46266</v>
+        <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45428</v>
+        <v>45587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45222</v>
+        <v>45146</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46248</v>
+        <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45616</v>
+        <v>45637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46248</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45594</v>
+        <v>45724</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45712</v>
+        <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45085</v>
+        <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45737</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46037</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46038</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45594</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45208</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46135</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45222</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46128</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>46160</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45026</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46266</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45372</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46238</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>44769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45146</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45724</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45737</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46037</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46038</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>45803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45594</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45208</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46135</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45222</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>44838</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45428</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45642</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46128</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>46160</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45446</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>45594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>44680</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>46185</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45026</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>45616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46266</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45372</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46238</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>44769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45146</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45724</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45737</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,13 +1233,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46037</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1312,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1369,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46038</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1385,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1428,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1438,14 +1433,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45803</v>
+        <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1457,13 +1452,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1589,14 +1579,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1608,13 +1598,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1657,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1671,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45922</v>
+        <v>44680</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1687,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1744,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45169</v>
+        <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1760,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1803,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1817,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45594</v>
+        <v>44489</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46092</v>
+        <v>45798</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45208</v>
+        <v>45146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46099</v>
+        <v>44769</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>46092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46135</v>
+        <v>46099</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2251,14 +2236,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45406</v>
+        <v>45055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46136</v>
+        <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45222</v>
+        <v>44838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45810</v>
+        <v>46136</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46136</v>
+        <v>45587</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44838</v>
+        <v>45637</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2694,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46149</v>
+        <v>46135</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2767,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2810,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2824,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45428</v>
+        <v>45737</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2854,8 +2839,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45642</v>
+        <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2918,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46128</v>
+        <v>44907</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46160</v>
+        <v>46038</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45055</v>
+        <v>46136</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45446</v>
+        <v>45406</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45798</v>
+        <v>45594</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3346,14 +3336,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46176</v>
+        <v>45640</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45594</v>
+        <v>45026</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45673</v>
+        <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44680</v>
+        <v>46160</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46185</v>
+        <v>45642</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45026</v>
+        <v>46128</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46195</v>
+        <v>45372</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45616</v>
+        <v>46176</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46203</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45673</v>
+        <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46266</v>
+        <v>45724</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45372</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4212,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46238</v>
+        <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44907</v>
+        <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44769</v>
+        <v>45222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46248</v>
+        <v>46266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45587</v>
+        <v>46238</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45146</v>
+        <v>45616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46248</v>
+        <v>45594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45085</v>
+        <v>45712</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45637</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4873,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>45085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4889,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4932,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4946,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45724</v>
+        <v>46248</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4962,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5005,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5015,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5044,8 +5034,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5083,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5093,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44489</v>
+        <v>45803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5117,8 +5112,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1306,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1360,14 +1365,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1384,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1440,7 +1450,7 @@
         <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1496,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45673</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,14 +1589,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45169</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1609,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1666,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44680</v>
+        <v>45594</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1732,7 +1742,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1788,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1812,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44489</v>
+        <v>46092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45798</v>
+        <v>45208</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1944,14 +1954,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45146</v>
+        <v>45838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1974,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44769</v>
+        <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46092</v>
+        <v>46112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46099</v>
+        <v>45798</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45673</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2323,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45055</v>
+        <v>46135</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45673</v>
+        <v>45406</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44838</v>
+        <v>46136</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46136</v>
+        <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45587</v>
+        <v>46136</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2631,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45637</v>
+        <v>45737</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2693,8 +2703,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2767,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2810,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45737</v>
+        <v>45642</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2839,13 +2854,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45810</v>
+        <v>46128</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44907</v>
+        <v>46160</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46038</v>
+        <v>46176</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46136</v>
+        <v>46185</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45406</v>
+        <v>45222</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45594</v>
+        <v>46195</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3336,14 +3346,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45640</v>
+        <v>44838</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45026</v>
+        <v>45428</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46149</v>
+        <v>46203</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46160</v>
+        <v>45055</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45642</v>
+        <v>45446</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46128</v>
+        <v>45594</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45372</v>
+        <v>46266</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46176</v>
+        <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46185</v>
+        <v>45026</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46195</v>
+        <v>45616</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45724</v>
+        <v>45673</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45169</v>
+        <v>46238</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46203</v>
+        <v>45372</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>46248</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45222</v>
+        <v>44907</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46266</v>
+        <v>44769</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45616</v>
+        <v>45587</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45594</v>
+        <v>45146</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45712</v>
+        <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46248</v>
+        <v>45637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4873,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45085</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4889,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4932,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4946,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46248</v>
+        <v>45724</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4962,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5005,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5015,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5034,13 +5044,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5083,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5093,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45803</v>
+        <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5112,13 +5117,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45208</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>45085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1365,14 +1360,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45673</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1384,13 +1379,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1433,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46037</v>
+        <v>44838</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46038</v>
+        <v>45587</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45169</v>
+        <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1666,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45594</v>
+        <v>45637</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1725,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1739,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45922</v>
+        <v>45446</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1755,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46092</v>
+        <v>44862</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1828,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,14 +1871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45208</v>
+        <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1900,8 +1890,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1944,7 +1939,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1954,14 +1949,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45838</v>
+        <v>45803</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1973,8 +1968,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46099</v>
+        <v>44907</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46112</v>
+        <v>45922</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45798</v>
+        <v>45527</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45673</v>
+        <v>45594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46135</v>
+        <v>45640</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45406</v>
+        <v>45026</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46136</v>
+        <v>45838</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45810</v>
+        <v>44680</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46136</v>
+        <v>45798</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45737</v>
+        <v>45372</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2703,13 +2703,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2777,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2834,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45642</v>
+        <v>45406</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2907,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46128</v>
+        <v>44489</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46160</v>
+        <v>46149</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +2996,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3039,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46176</v>
+        <v>45146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46185</v>
+        <v>46160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3190,7 +3185,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45222</v>
+        <v>45642</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3215,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3258,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3272,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46195</v>
+        <v>46128</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3288,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3331,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44838</v>
+        <v>45737</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3365,8 +3360,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45428</v>
+        <v>45724</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46203</v>
+        <v>45169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45055</v>
+        <v>44769</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45446</v>
+        <v>46176</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45594</v>
+        <v>46038</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46266</v>
+        <v>46037</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44680</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45026</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45616</v>
+        <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45673</v>
+        <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46238</v>
+        <v>46203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45372</v>
+        <v>46092</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46248</v>
+        <v>46099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44907</v>
+        <v>46112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44769</v>
+        <v>45616</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46248</v>
+        <v>46136</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45587</v>
+        <v>46135</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45146</v>
+        <v>45810</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45085</v>
+        <v>46266</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45637</v>
+        <v>45594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4886,7 +4886,7 @@
         <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45724</v>
+        <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44862</v>
+        <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44489</v>
+        <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45055</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45208</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45085</v>
+        <v>45838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45673</v>
+        <v>45169</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44838</v>
+        <v>45594</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45587</v>
+        <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45673</v>
+        <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45637</v>
+        <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45446</v>
+        <v>45673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44862</v>
+        <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45803</v>
+        <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1890,13 +1890,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1939,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1949,14 +1944,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45803</v>
+        <v>46112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1968,13 +1963,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44907</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45922</v>
+        <v>44838</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45527</v>
+        <v>46135</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45594</v>
+        <v>45428</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2319,14 +2309,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45640</v>
+        <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45026</v>
+        <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2465,14 +2455,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45838</v>
+        <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44680</v>
+        <v>45737</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2557,8 +2547,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2596,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2610,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45798</v>
+        <v>45810</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2631,7 +2626,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2669,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2683,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45372</v>
+        <v>45446</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2704,7 +2699,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2742,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2764,7 +2759,7 @@
         <v>46136</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2820,7 +2815,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2834,10 +2829,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45406</v>
+        <v>46037</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2845,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44489</v>
+        <v>46038</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2918,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46149</v>
+        <v>45594</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2996,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3039,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3053,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45146</v>
+        <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3069,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46160</v>
+        <v>45026</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3142,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3185,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45642</v>
+        <v>45616</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3215,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3258,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3272,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46128</v>
+        <v>46149</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3288,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3331,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3345,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45737</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3360,13 +3355,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45724</v>
+        <v>45642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45169</v>
+        <v>46128</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44769</v>
+        <v>46160</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46176</v>
+        <v>45372</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46038</v>
+        <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46037</v>
+        <v>44907</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>44769</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3937,7 +3927,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3993,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45222</v>
+        <v>46195</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46203</v>
+        <v>45587</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4159,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46092</v>
+        <v>45146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46099</v>
+        <v>45085</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46112</v>
+        <v>46266</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45616</v>
+        <v>45637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46136</v>
+        <v>45712</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46135</v>
+        <v>45724</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45810</v>
+        <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46266</v>
+        <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4800,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45594</v>
+        <v>46238</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4879,14 +4869,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4898,8 +4888,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4937,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4947,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46238</v>
+        <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4971,8 +4966,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8183-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44609</v>
+        <v>44861</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 42169-2022</t>
+          <t>A 8183-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44830</v>
+        <v>44609</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 42169-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>44830</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45587</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45838</v>
+        <v>45616</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45169</v>
+        <v>45446</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45594</v>
+        <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45208</v>
+        <v>44907</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46092</v>
+        <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>44862</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45673</v>
+        <v>45594</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46099</v>
+        <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45922</v>
+        <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46112</v>
+        <v>45712</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45222</v>
+        <v>45594</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44838</v>
+        <v>45085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2163,14 +2163,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46135</v>
+        <v>45640</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45428</v>
+        <v>45026</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45406</v>
+        <v>45922</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46136</v>
+        <v>44680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2455,14 +2455,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45055</v>
+        <v>45803</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2474,8 +2474,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2523,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2528,14 +2533,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45737</v>
+        <v>45803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2549,11 +2554,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2596,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2610,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45810</v>
+        <v>45372</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2626,7 +2631,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2669,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2683,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45446</v>
+        <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2699,7 +2704,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2742,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2756,10 +2761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46136</v>
+        <v>45146</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2772,7 +2777,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2815,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2825,14 +2830,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46037</v>
+        <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2845,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2902,10 +2907,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46038</v>
+        <v>44769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45594</v>
+        <v>45724</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +2996,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3039,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3053,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44680</v>
+        <v>45169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3064,7 +3069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45026</v>
+        <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3142,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3185,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3199,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45616</v>
+        <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3215,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3258,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3272,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46149</v>
+        <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3288,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3331,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3345,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3361,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3404,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3418,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45642</v>
+        <v>44838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3434,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3477,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46128</v>
+        <v>46112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3507,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3550,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3564,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46160</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3580,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3623,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3637,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45372</v>
+        <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3653,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3696,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3710,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46176</v>
+        <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3726,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3769,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3783,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44907</v>
+        <v>45810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3842,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3856,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44769</v>
+        <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3866,8 +3871,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46185</v>
+        <v>46136</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46195</v>
+        <v>45406</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46203</v>
+        <v>46038</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45587</v>
+        <v>46037</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.9</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45146</v>
+        <v>46149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45085</v>
+        <v>46160</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46266</v>
+        <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45637</v>
+        <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45712</v>
+        <v>46092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45724</v>
+        <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44862</v>
+        <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44489</v>
+        <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46238</v>
+        <v>46203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4869,14 +4879,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45803</v>
+        <v>46266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4888,13 +4898,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4937,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4947,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45803</v>
+        <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4966,13 +4971,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44861</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44609</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44830</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45587</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45616</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45446</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>44907</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44862</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45594</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45712</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45594</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45640</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45026</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45922</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45803</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>45803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45372</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45146</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45724</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46136</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45406</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46038</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>46037</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>46160</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>46092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44861</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44609</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44830</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45587</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45637</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45616</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45446</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>44907</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44862</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45594</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45712</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45594</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45085</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45640</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45026</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45922</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>44680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45803</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>45803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45372</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>44489</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45146</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44769</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45724</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45169</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>45055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>45673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44838</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45810</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46136</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45406</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>46038</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>46037</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>46160</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45642</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>46128</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>46092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46176</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>46185</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>46203</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>46266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46248</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 8183-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44861</v>
+        <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8183-2022</t>
+          <t>A 42169-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44609</v>
+        <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 42169-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44830</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45587</v>
+        <v>46176</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45637</v>
+        <v>45085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45616</v>
+        <v>45922</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45446</v>
+        <v>45637</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45208</v>
+        <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44907</v>
+        <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45798</v>
+        <v>45724</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44862</v>
+        <v>46195</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45594</v>
+        <v>44862</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45673</v>
+        <v>44489</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45527</v>
+        <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1944,14 +1944,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45712</v>
+        <v>45640</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45594</v>
+        <v>46266</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2090,14 +2090,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45085</v>
+        <v>45803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2109,8 +2109,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2158,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2163,14 +2168,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45640</v>
+        <v>45803</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2182,8 +2187,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45026</v>
+        <v>45737</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2255,8 +2265,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45922</v>
+        <v>46238</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2382,14 +2397,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44680</v>
+        <v>45838</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2455,14 +2470,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45803</v>
+        <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2474,13 +2489,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2523,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2533,14 +2543,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45803</v>
+        <v>46038</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2552,13 +2562,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45372</v>
+        <v>46248</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2631,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44489</v>
+        <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2704,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45146</v>
+        <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2777,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2820,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2830,14 +2835,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45838</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2907,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44769</v>
+        <v>46248</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45724</v>
+        <v>46099</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2996,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3039,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45169</v>
+        <v>46112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3069,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45055</v>
+        <v>46135</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3142,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3185,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46099</v>
+        <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3215,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3258,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3272,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45673</v>
+        <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3288,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3331,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3345,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45428</v>
+        <v>46136</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3404,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3418,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44838</v>
+        <v>45810</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3434,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3477,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3491,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46112</v>
+        <v>46136</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3507,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3550,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3564,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45169</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3580,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3623,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3637,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46136</v>
+        <v>45594</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3653,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3696,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3726,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3769,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3783,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45810</v>
+        <v>45208</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3799,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3842,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3856,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45737</v>
+        <v>45642</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3871,13 +3876,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46136</v>
+        <v>46128</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45406</v>
+        <v>46160</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46038</v>
+        <v>45222</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46037</v>
+        <v>44838</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46149</v>
+        <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46160</v>
+        <v>45055</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45642</v>
+        <v>45446</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46128</v>
+        <v>45594</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46092</v>
+        <v>44680</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46176</v>
+        <v>45026</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46185</v>
+        <v>45616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46195</v>
+        <v>45673</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46203</v>
+        <v>45372</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46266</v>
+        <v>44907</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46238</v>
+        <v>44769</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46248</v>
+        <v>45587</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46248</v>
+        <v>45146</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46176</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45085</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45922</v>
+        <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1306,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1369,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45637</v>
+        <v>44862</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1385,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1428,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1442,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45712</v>
+        <v>45673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1458,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1501,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1506,14 +1511,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46185</v>
+        <v>45803</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1525,8 +1530,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,14 +1589,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45724</v>
+        <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1598,8 +1608,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1657,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1671,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46195</v>
+        <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1687,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44862</v>
+        <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1760,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1798,14 +1813,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44489</v>
+        <v>45838</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1833,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1890,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46203</v>
+        <v>46038</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1906,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1944,14 +1959,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45640</v>
+        <v>46037</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46266</v>
+        <v>44680</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2090,14 +2105,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45803</v>
+        <v>45798</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2109,13 +2124,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2158,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2168,14 +2178,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45803</v>
+        <v>44489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2187,13 +2197,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45737</v>
+        <v>45146</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2265,13 +2270,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46238</v>
+        <v>44769</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45838</v>
+        <v>46092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46037</v>
+        <v>46099</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46038</v>
+        <v>45055</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46248</v>
+        <v>45673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45798</v>
+        <v>46112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45673</v>
+        <v>44838</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>45587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46248</v>
+        <v>45637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46099</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46112</v>
+        <v>46135</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46135</v>
+        <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45527</v>
+        <v>44907</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45406</v>
+        <v>46136</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46136</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45810</v>
+        <v>45594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3492,14 +3492,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46136</v>
+        <v>45640</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45169</v>
+        <v>45026</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45594</v>
+        <v>46149</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46149</v>
+        <v>46160</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45208</v>
+        <v>45642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45642</v>
+        <v>46128</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46128</v>
+        <v>45372</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45222</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44838</v>
+        <v>45724</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45428</v>
+        <v>45169</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45055</v>
+        <v>46195</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45446</v>
+        <v>45428</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45594</v>
+        <v>46203</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44680</v>
+        <v>45222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45026</v>
+        <v>45616</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45616</v>
+        <v>46238</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45673</v>
+        <v>45594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45372</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44907</v>
+        <v>45712</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44769</v>
+        <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45587</v>
+        <v>46248</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45146</v>
+        <v>46308</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,24 +5161,24 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S 2400-2022</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44690</v>
+        <v>46266</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5234,85 +5234,80 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
+          <t>S 2400-2022</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>44690</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>GRÄSTORP</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>S 1654-2025</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E65" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>S 1657-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5329,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5347,45 +5342,123 @@
         </is>
       </c>
       <c r="I66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>S 1657-2025</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>45803</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>GRÄSTORP</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
         <v>3.3</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>45222</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45803</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1160,8 +1160,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1209,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1219,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1238,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1287,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1301,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45737</v>
+        <v>44811</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,13 +1316,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1365,14 +1370,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44862</v>
+        <v>45640</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1385,7 +1390,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1428,7 +1433,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1442,10 +1447,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45673</v>
+        <v>44838</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1458,7 +1463,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1501,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1511,14 +1516,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1530,13 +1535,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1589,14 +1589,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45803</v>
+        <v>45798</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1608,13 +1608,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1657,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1671,10 +1666,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45527</v>
+        <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1687,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1725,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1744,10 +1739,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45922</v>
+        <v>45673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1760,7 +1755,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1803,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,14 +1808,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45838</v>
+        <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46038</v>
+        <v>45428</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1958,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46037</v>
+        <v>46092</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1974,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44680</v>
+        <v>46099</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45798</v>
+        <v>45169</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44489</v>
+        <v>45594</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45146</v>
+        <v>46112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2323,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44769</v>
+        <v>45208</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46092</v>
+        <v>45055</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46099</v>
+        <v>46135</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45055</v>
+        <v>45406</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45673</v>
+        <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2635,8 +2630,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46112</v>
+        <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44838</v>
+        <v>46037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45587</v>
+        <v>45810</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45637</v>
+        <v>46038</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45810</v>
+        <v>45446</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44907</v>
+        <v>45594</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46136</v>
+        <v>45642</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>46128</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45594</v>
+        <v>46160</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3492,14 +3492,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45640</v>
+        <v>44680</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>45026</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46149</v>
+        <v>45616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45642</v>
+        <v>46185</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46128</v>
+        <v>45673</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45372</v>
+        <v>46195</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46176</v>
+        <v>46203</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46185</v>
+        <v>45372</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45724</v>
+        <v>44907</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45169</v>
+        <v>44769</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46195</v>
+        <v>46238</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45428</v>
+        <v>45587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46203</v>
+        <v>45146</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45222</v>
+        <v>46248</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45616</v>
+        <v>45085</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46238</v>
+        <v>45637</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45594</v>
+        <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46248</v>
+        <v>45712</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45712</v>
+        <v>45724</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45085</v>
+        <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46248</v>
+        <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>46308</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>46266</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45222</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         <v>45803</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1219,14 +1219,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45803</v>
+        <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1238,13 +1238,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1287,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1297,14 +1292,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44811</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1316,8 +1311,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1370,14 +1370,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45640</v>
+        <v>45673</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>44838</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45838</v>
+        <v>45208</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45798</v>
+        <v>45587</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45922</v>
+        <v>45637</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45673</v>
+        <v>45446</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45428</v>
+        <v>45838</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46092</v>
+        <v>44862</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46099</v>
+        <v>44907</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45169</v>
+        <v>45527</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45594</v>
+        <v>45798</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46112</v>
+        <v>45594</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45055</v>
+        <v>46099</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46135</v>
+        <v>45026</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45406</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45737</v>
+        <v>44680</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2630,13 +2630,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,7 +2691,7 @@
         <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2752,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46037</v>
+        <v>46135</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2777,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2834,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45810</v>
+        <v>45372</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2907,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46038</v>
+        <v>45810</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>44489</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +2996,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3039,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3053,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46149</v>
+        <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3069,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45446</v>
+        <v>45146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3142,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3185,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45594</v>
+        <v>45406</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3215,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3258,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3272,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45642</v>
+        <v>44769</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3288,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3331,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3345,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46128</v>
+        <v>46149</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3361,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3404,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3418,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46160</v>
+        <v>45724</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3434,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3477,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3491,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44680</v>
+        <v>45169</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3507,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3550,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3564,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45026</v>
+        <v>45922</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3580,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3623,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3637,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45616</v>
+        <v>46160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3653,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3696,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46176</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3726,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3769,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46185</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3799,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3842,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3856,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45673</v>
+        <v>45428</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3872,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3915,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3929,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46195</v>
+        <v>46176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3945,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3988,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4002,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46203</v>
+        <v>45222</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4018,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4061,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4075,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45372</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4139,7 +4134,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4148,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44907</v>
+        <v>46195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4164,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4207,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4221,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44769</v>
+        <v>46203</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4237,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4280,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4294,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46238</v>
+        <v>45616</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4310,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4353,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4367,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45587</v>
+        <v>45594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4383,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4426,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4440,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45146</v>
+        <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4456,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4499,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4513,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46248</v>
+        <v>45712</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4529,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4594,7 +4589,7 @@
         <v>45085</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4645,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4659,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45637</v>
+        <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4675,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4740,7 +4735,7 @@
         <v>46248</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4796,7 +4791,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4805,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45712</v>
+        <v>45737</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4825,8 +4820,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45724</v>
+        <v>46038</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44862</v>
+        <v>46037</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44489</v>
+        <v>46308</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46308</v>
+        <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46266</v>
+        <v>46092</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45055</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45803</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1160,13 +1160,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1209,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1223,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44811</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>45169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1311,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1360,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1374,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45673</v>
+        <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1390,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1433,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44838</v>
+        <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45208</v>
+        <v>45406</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45587</v>
+        <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1666,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45637</v>
+        <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1725,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1739,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45446</v>
+        <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1755,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45673</v>
+        <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1828,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1881,14 +1871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45838</v>
+        <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1901,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1944,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1958,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44862</v>
+        <v>46149</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1974,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44907</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45527</v>
+        <v>44838</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45798</v>
+        <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45594</v>
+        <v>46128</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2319,14 +2309,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45640</v>
+        <v>46160</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46099</v>
+        <v>45428</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45026</v>
+        <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46112</v>
+        <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44680</v>
+        <v>45594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2631,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2688,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46136</v>
+        <v>45737</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2703,8 +2693,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2742,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2761,10 +2756,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46135</v>
+        <v>44680</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2777,7 +2772,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2820,7 +2815,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2834,10 +2829,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45372</v>
+        <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2845,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45810</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2918,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44489</v>
+        <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2996,7 +2991,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3039,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3053,10 +3048,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46136</v>
+        <v>45026</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3069,7 +3064,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45146</v>
+        <v>45616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3142,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3185,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45406</v>
+        <v>46185</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3215,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3258,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3272,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44769</v>
+        <v>46092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3288,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3331,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3345,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46149</v>
+        <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3361,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3404,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3418,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45724</v>
+        <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3434,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3477,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45169</v>
+        <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3507,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3550,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3564,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45922</v>
+        <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3580,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3623,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3637,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46160</v>
+        <v>45372</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3696,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3710,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3726,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3769,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3783,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>46203</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3842,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3856,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45428</v>
+        <v>44907</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3872,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3915,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3929,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46176</v>
+        <v>44769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3945,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3988,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45222</v>
+        <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4018,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4061,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4075,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46185</v>
+        <v>46238</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4091,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4134,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4148,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46195</v>
+        <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4164,7 +4159,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4207,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4221,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46203</v>
+        <v>45085</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4237,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4280,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4294,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45616</v>
+        <v>45637</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4310,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4353,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4367,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45594</v>
+        <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4383,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4426,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4440,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46238</v>
+        <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4456,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4499,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45712</v>
+        <v>45724</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4529,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4572,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4586,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45085</v>
+        <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4602,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4645,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4662,7 +4657,7 @@
         <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4675,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4718,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4732,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46248</v>
+        <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4748,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4791,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4801,14 +4796,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45737</v>
+        <v>46308</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4820,13 +4815,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4859,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4879,14 +4869,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46038</v>
+        <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4898,8 +4888,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4937,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4947,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46037</v>
+        <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4971,8 +4966,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46308</v>
+        <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46266</v>
+        <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46092</v>
+        <v>45798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45406</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>46149</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44838</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>46128</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46160</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45428</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45737</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44680</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45026</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>46185</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45372</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46203</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44907</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>46238</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45085</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45637</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45724</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46308</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45169</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45594</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45208</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45406</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>45922</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>46149</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44838</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45642</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>46128</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>46160</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>45428</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45055</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>45446</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45594</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45737</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>44680</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>45026</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>46185</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>46092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>45673</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>46195</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45372</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>46135</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>46203</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44907</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>44769</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>45587</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>46238</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45146</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45085</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>45637</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>45712</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>45724</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>44862</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46308</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45169</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45594</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45208</v>
+        <v>44680</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 58914-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45406</v>
+        <v>44489</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45673</v>
+        <v>45146</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46136</v>
+        <v>45798</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45810</v>
+        <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46136</v>
+        <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45922</v>
+        <v>45406</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46149</v>
+        <v>44769</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45222</v>
+        <v>45922</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44838</v>
+        <v>45055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45642</v>
+        <v>45673</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46128</v>
+        <v>44838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46160</v>
+        <v>45587</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45428</v>
+        <v>45637</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45055</v>
+        <v>46149</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45446</v>
+        <v>44907</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45594</v>
+        <v>46160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45737</v>
+        <v>45642</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2693,13 +2693,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2742,7 +2737,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2756,10 +2751,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44680</v>
+        <v>46128</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2772,7 +2767,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2815,7 +2810,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2829,10 +2824,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46176</v>
+        <v>45594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2845,7 +2840,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.300000000000001</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2888,7 +2883,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2898,14 +2893,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>45640</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2918,7 +2913,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2961,7 +2956,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2970,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46038</v>
+        <v>45026</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +2986,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3029,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3048,10 +3043,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45026</v>
+        <v>45737</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3063,8 +3058,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3107,7 +3107,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45616</v>
+        <v>46038</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46185</v>
+        <v>46037</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46092</v>
+        <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45673</v>
+        <v>45372</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3399,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46099</v>
+        <v>46185</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46195</v>
+        <v>46092</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46112</v>
+        <v>46099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45372</v>
+        <v>46195</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46135</v>
+        <v>45724</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3764,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46203</v>
+        <v>45169</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44907</v>
+        <v>46112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3910,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44769</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45587</v>
+        <v>46203</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46238</v>
+        <v>46136</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45146</v>
+        <v>46135</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45085</v>
+        <v>45810</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45637</v>
+        <v>45222</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4348,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46248</v>
+        <v>45616</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4435,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45712</v>
+        <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45724</v>
+        <v>45594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44862</v>
+        <v>46248</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46248</v>
+        <v>45712</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44489</v>
+        <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>7.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4786,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46308</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>45803</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>45803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46266</v>
+        <v>46308</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>46266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5171,14 +5171,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45798</v>
+        <v>45838</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>44690</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE67"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1292,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1311,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1374,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>45737</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1389,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1438,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1452,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44680</v>
+        <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1468,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1511,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58914-2021</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1525,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44489</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1541,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1584,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1598,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45146</v>
+        <v>45527</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1614,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1657,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1671,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45798</v>
+        <v>45922</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1715,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46136</v>
+        <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1760,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1817,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45673</v>
+        <v>46092</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1833,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1890,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45406</v>
+        <v>45594</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1906,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44769</v>
+        <v>46099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1964,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45922</v>
+        <v>46112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45055</v>
+        <v>45208</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2163,14 +2178,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45673</v>
+        <v>45838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44838</v>
+        <v>46135</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45587</v>
+        <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45637</v>
+        <v>46136</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2459,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46149</v>
+        <v>45810</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44907</v>
+        <v>46136</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2591,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2605,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46160</v>
+        <v>45222</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2621,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2664,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2678,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45642</v>
+        <v>45798</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2694,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2737,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2751,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46128</v>
+        <v>45673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2810,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2824,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45594</v>
+        <v>46149</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2840,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2883,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2893,14 +2908,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45640</v>
+        <v>44838</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2913,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2956,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2970,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45026</v>
+        <v>45642</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2986,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3029,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3043,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45737</v>
+        <v>46128</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3056,11 +3071,6 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3107,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46038</v>
+        <v>46160</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3137,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3180,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3194,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46037</v>
+        <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3210,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3253,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3267,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46176</v>
+        <v>45055</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3283,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3326,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3340,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45372</v>
+        <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3356,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3399,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3413,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46185</v>
+        <v>45446</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3429,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3472,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3486,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46092</v>
+        <v>46185</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3502,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3545,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 48864-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3559,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46099</v>
+        <v>45594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3575,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3635,7 +3645,7 @@
         <v>46195</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3691,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3705,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45724</v>
+        <v>44680</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3764,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3778,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45169</v>
+        <v>45026</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3794,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3837,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3851,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46112</v>
+        <v>45616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3867,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3910,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3924,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45428</v>
+        <v>46203</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3940,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3983,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46203</v>
+        <v>45673</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4013,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4056,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4070,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46136</v>
+        <v>46238</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4086,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4129,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4143,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46135</v>
+        <v>45372</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4159,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4202,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4216,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45810</v>
+        <v>46248</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4232,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4275,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4289,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45222</v>
+        <v>44907</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4305,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4348,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4362,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45616</v>
+        <v>44769</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4378,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4421,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4435,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4451,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4494,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4508,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45594</v>
+        <v>45587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4524,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4567,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4581,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46248</v>
+        <v>45146</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4597,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4640,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4650,14 +4660,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45712</v>
+        <v>46308</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4670,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4713,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4727,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45085</v>
+        <v>46266</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4743,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4786,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4800,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46248</v>
+        <v>45085</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4816,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4859,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4869,14 +4879,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45803</v>
+        <v>45637</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4888,13 +4898,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4937,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4947,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45803</v>
+        <v>45712</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4966,13 +4971,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46308</v>
+        <v>45724</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5102,10 +5102,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46266</v>
+        <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,24 +5161,24 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>S 2400-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45838</v>
+        <v>44690</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S 2400-2022</t>
+          <t>S 1654-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44690</v>
+        <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5263,8 +5263,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5304,10 +5309,10 @@
       </c>
       <c r="V65" s="2" t="inlineStr"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S 1654-2025</t>
+          <t>S 1657-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5324,7 +5329,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5342,7 +5347,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5381,84 +5386,6 @@
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>S 1657-2025</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E67" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45640</v>
+        <v>45208</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45803</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,13 +1233,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1282,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1292,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>44862</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1311,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1360,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1374,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45737</v>
+        <v>45673</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1387,11 +1377,6 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1438,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1452,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46037</v>
+        <v>45737</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1467,8 +1452,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1511,7 +1501,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,10 +1515,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46038</v>
+        <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1541,7 +1531,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1584,7 +1574,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1594,14 +1584,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45527</v>
+        <v>45803</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1613,8 +1603,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1657,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1667,14 +1662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45922</v>
+        <v>45803</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1686,8 +1681,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45169</v>
+        <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1803,7 +1803,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,14 +1813,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46092</v>
+        <v>45838</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45594</v>
+        <v>44680</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46099</v>
+        <v>46038</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46112</v>
+        <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45208</v>
+        <v>45798</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2178,14 +2178,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45838</v>
+        <v>45146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46135</v>
+        <v>44769</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45406</v>
+        <v>45055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46136</v>
+        <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45810</v>
+        <v>46092</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46136</v>
+        <v>44838</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45222</v>
+        <v>46099</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45798</v>
+        <v>45587</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45673</v>
+        <v>45637</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46149</v>
+        <v>46112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44838</v>
+        <v>44907</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45642</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46128</v>
+        <v>46135</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46160</v>
+        <v>45810</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45428</v>
+        <v>46136</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45055</v>
+        <v>45640</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46176</v>
+        <v>45026</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45446</v>
+        <v>45406</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46185</v>
+        <v>46149</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48864-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45594</v>
+        <v>45372</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46195</v>
+        <v>46160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44680</v>
+        <v>45642</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45026</v>
+        <v>46128</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45616</v>
+        <v>46176</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46203</v>
+        <v>45724</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45673</v>
+        <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46238</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45372</v>
+        <v>46195</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46248</v>
+        <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44907</v>
+        <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44769</v>
+        <v>45222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45587</v>
+        <v>45616</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45146</v>
+        <v>45594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4660,14 +4660,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46308</v>
+        <v>46248</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46266</v>
+        <v>45712</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>45085</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45637</v>
+        <v>46248</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>7.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45712</v>
+        <v>46308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45724</v>
+        <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5088,24 +5088,24 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>S 2400-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44862</v>
+        <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S 2400-2022</t>
+          <t>S 1654-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5171,14 +5171,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44690</v>
+        <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5190,8 +5190,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5231,10 +5236,10 @@
       </c>
       <c r="V64" s="2" t="inlineStr"/>
     </row>
-    <row r="65" ht="15" customHeight="1">
+    <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S 1654-2025</t>
+          <t>S 1657-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5251,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5269,7 +5274,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5308,84 +5313,6 @@
         <v>0</v>
       </c>
       <c r="V65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>S 1657-2025</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>45803</v>
-      </c>
-      <c r="E66" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45208</v>
+        <v>45026</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45616</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44862</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1306,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1360,14 +1365,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45673</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1384,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1433,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1433,14 +1443,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45737</v>
+        <v>45640</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1452,13 +1462,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1501,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1515,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1531,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1574,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1584,14 +1589,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45803</v>
+        <v>45838</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1603,13 +1608,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1662,14 +1662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45803</v>
+        <v>45372</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1681,13 +1681,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1747,7 +1742,7 @@
         <v>45922</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1803,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,14 +1808,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45838</v>
+        <v>45798</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1890,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44680</v>
+        <v>44907</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1906,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1949,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,10 +1958,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46038</v>
+        <v>44769</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1979,7 +1974,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2022,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46037</v>
+        <v>45673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2052,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2095,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2109,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45798</v>
+        <v>45406</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2125,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2168,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2182,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45146</v>
+        <v>46136</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2198,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44769</v>
+        <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2323,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45055</v>
+        <v>46136</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45673</v>
+        <v>45587</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46092</v>
+        <v>45146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44838</v>
+        <v>46149</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2601,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46099</v>
+        <v>45642</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2636,7 +2631,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2688,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45587</v>
+        <v>45085</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2704,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2747,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45637</v>
+        <v>46128</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2777,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2820,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2834,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46112</v>
+        <v>46160</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2850,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2893,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2907,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44907</v>
+        <v>45637</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2923,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2966,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2980,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>45737</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3000,8 +2995,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46135</v>
+        <v>45712</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45810</v>
+        <v>45724</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46136</v>
+        <v>46037</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3273,14 +3273,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45640</v>
+        <v>46038</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45026</v>
+        <v>46176</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45406</v>
+        <v>44862</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46149</v>
+        <v>45527</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45372</v>
+        <v>46185</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46160</v>
+        <v>46195</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45642</v>
+        <v>46092</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46176</v>
+        <v>46203</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45724</v>
+        <v>46112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
         <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46185</v>
+        <v>45594</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46195</v>
+        <v>46135</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45428</v>
+        <v>45208</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46203</v>
+        <v>46238</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45222</v>
+        <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45616</v>
+        <v>45222</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45594</v>
+        <v>44838</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46248</v>
+        <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45712</v>
+        <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45085</v>
+        <v>46266</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46248</v>
+        <v>45055</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46308</v>
+        <v>45446</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46266</v>
+        <v>44680</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45026</v>
+        <v>45673</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45616</v>
+        <v>45208</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45803</v>
+        <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,13 +1306,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1365,14 +1360,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1384,13 +1379,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1433,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1443,14 +1433,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45640</v>
+        <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45673</v>
+        <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1589,14 +1579,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45838</v>
+        <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1666,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45372</v>
+        <v>46176</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1725,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1739,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45922</v>
+        <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1755,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1798,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1812,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45798</v>
+        <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1828,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1871,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1885,10 +1875,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44907</v>
+        <v>46195</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1901,7 +1891,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1944,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1958,10 +1948,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44769</v>
+        <v>45594</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1974,7 +1964,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45673</v>
+        <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45406</v>
+        <v>45712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46136</v>
+        <v>44862</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2183,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2240,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45810</v>
+        <v>45085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>7.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2323,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46136</v>
+        <v>45737</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2338,8 +2328,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2377,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2391,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45587</v>
+        <v>46238</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2407,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2450,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45146</v>
+        <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2485,7 +2480,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2528,7 +2523,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2537,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46149</v>
+        <v>46037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2553,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2596,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2611,14 +2606,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45642</v>
+        <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2630,8 +2625,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,14 +2684,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45085</v>
+        <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2703,8 +2703,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2747,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46128</v>
+        <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2777,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2820,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2830,14 +2835,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46160</v>
+        <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2850,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2893,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2907,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45637</v>
+        <v>46248</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2923,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>7.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2966,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2980,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45737</v>
+        <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2995,13 +3000,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45712</v>
+        <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45724</v>
+        <v>46099</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46037</v>
+        <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46038</v>
+        <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46176</v>
+        <v>46136</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44862</v>
+        <v>46308</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45527</v>
+        <v>46266</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46185</v>
+        <v>46135</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46195</v>
+        <v>45810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46092</v>
+        <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46099</v>
+        <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46203</v>
+        <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46112</v>
+        <v>46149</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45169</v>
+        <v>45146</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45594</v>
+        <v>44769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46135</v>
+        <v>45055</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45208</v>
+        <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46238</v>
+        <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46248</v>
+        <v>45587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46248</v>
+        <v>45637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45222</v>
+        <v>44907</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44838</v>
+        <v>45640</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45428</v>
+        <v>45026</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46308</v>
+        <v>45372</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46266</v>
+        <v>45724</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45055</v>
+        <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45446</v>
+        <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44680</v>
+        <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45673</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45208</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46176</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>46195</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45594</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>44862</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45737</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>46238</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>46248</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46099</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46136</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>46308</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>46266</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>46135</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46149</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45146</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>44769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45055</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44907</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45640</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45026</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>45372</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45724</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45673</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45208</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>45642</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>45922</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45446</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>46176</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45616</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>46185</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>46195</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45594</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45712</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>44862</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45737</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>46238</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46248</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45838</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>46248</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>46092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>46099</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>45798</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>46136</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>46308</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>46266</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>46135</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>45810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45406</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>46149</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45146</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>44769</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>45055</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>45673</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44838</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>45587</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44907</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45640</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45026</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>45372</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45724</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45222</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45673</v>
+        <v>46185</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45208</v>
+        <v>45640</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46160</v>
+        <v>45085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45642</v>
+        <v>45922</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46128</v>
+        <v>45637</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45922</v>
+        <v>45712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45446</v>
+        <v>45724</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46176</v>
+        <v>44862</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8.300000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45616</v>
+        <v>46195</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46185</v>
+        <v>45527</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46195</v>
+        <v>45803</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1890,8 +1890,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1939,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1944,14 +1949,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45594</v>
+        <v>45803</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1963,8 +1968,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2007,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46203</v>
+        <v>45169</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45712</v>
+        <v>45594</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44862</v>
+        <v>45737</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2182,8 +2192,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2241,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2236,14 +2251,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45085</v>
+        <v>45838</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2271,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2314,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2328,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45737</v>
+        <v>45208</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2326,11 +2341,6 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>GRÄSTORP</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2377,7 +2387,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2391,10 +2401,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46238</v>
+        <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2407,7 +2417,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2467,7 +2477,7 @@
         <v>46038</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2523,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2537,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46037</v>
+        <v>46203</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2553,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2596,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2606,14 +2616,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45803</v>
+        <v>45798</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2625,13 +2635,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2674,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,14 +2689,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45803</v>
+        <v>45673</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2703,13 +2708,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46248</v>
+        <v>45222</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2835,14 +2835,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45838</v>
+        <v>46092</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46248</v>
+        <v>46099</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46092</v>
+        <v>44838</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45527</v>
+        <v>46112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46099</v>
+        <v>46238</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46112</v>
+        <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45798</v>
+        <v>46135</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46136</v>
+        <v>45406</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3419,14 +3419,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46308</v>
+        <v>45055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46266</v>
+        <v>46136</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46135</v>
+        <v>45446</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         <v>45810</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3718,7 +3718,7 @@
         <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45406</v>
+        <v>44680</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44680</v>
+        <v>46248</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46149</v>
+        <v>45026</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45146</v>
+        <v>45616</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44769</v>
+        <v>46149</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45055</v>
+        <v>45642</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45673</v>
+        <v>46128</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44838</v>
+        <v>46160</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45587</v>
+        <v>45673</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.9</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45637</v>
+        <v>46176</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44907</v>
+        <v>46248</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4587,14 +4587,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45640</v>
+        <v>45372</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45026</v>
+        <v>44907</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45372</v>
+        <v>44769</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4806,14 +4806,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45724</v>
+        <v>46308</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45169</v>
+        <v>46266</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45428</v>
+        <v>45587</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45222</v>
+        <v>45146</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44861</v>
+        <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46185</v>
+        <v>45594</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45640</v>
+        <v>45146</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45085</v>
+        <v>45208</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45922</v>
+        <v>44769</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45637</v>
+        <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1496,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45712</v>
+        <v>45446</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45724</v>
+        <v>45673</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>44862</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46195</v>
+        <v>45055</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1788,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45803</v>
+        <v>44838</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1890,13 +1890,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1939,7 +1934,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1949,14 +1944,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45803</v>
+        <v>45922</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1968,13 +1963,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2017,7 +2007,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45169</v>
+        <v>45527</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2047,7 +2037,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2090,7 +2080,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2094,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45594</v>
+        <v>45587</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2153,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2167,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45737</v>
+        <v>45085</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2192,13 +2182,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2241,7 +2226,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2251,14 +2236,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45838</v>
+        <v>45637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2271,7 +2256,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2314,7 +2299,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2328,10 +2313,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45208</v>
+        <v>44907</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2344,7 +2329,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2387,7 +2372,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2401,10 +2386,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46037</v>
+        <v>44680</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2417,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2460,7 +2445,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2470,14 +2455,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46038</v>
+        <v>45640</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2490,7 +2475,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2533,7 +2518,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2547,10 +2532,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46203</v>
+        <v>45026</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2563,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2606,7 +2591,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2620,10 +2605,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45798</v>
+        <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2635,8 +2620,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2669,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2683,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45673</v>
+        <v>46203</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2699,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2742,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2756,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45222</v>
+        <v>45372</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2772,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2815,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2829,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46092</v>
+        <v>46038</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2845,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2888,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2902,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46099</v>
+        <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2918,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2961,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2975,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44838</v>
+        <v>46238</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3044,7 +3034,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3054,14 +3044,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46112</v>
+        <v>45803</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3073,8 +3063,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3112,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46238</v>
+        <v>45724</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3142,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3185,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3199,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45428</v>
+        <v>45169</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3215,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3258,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3273,14 +3268,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46135</v>
+        <v>45803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3292,8 +3287,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45406</v>
+        <v>46092</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45055</v>
+        <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46136</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45446</v>
+        <v>46248</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45810</v>
+        <v>46112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46136</v>
+        <v>45222</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44680</v>
+        <v>46248</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46248</v>
+        <v>46136</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45026</v>
+        <v>46135</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45616</v>
+        <v>45810</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4076,14 +4076,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46149</v>
+        <v>46308</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45642</v>
+        <v>46266</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46160</v>
+        <v>45406</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45673</v>
+        <v>45616</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46176</v>
+        <v>45838</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46248</v>
+        <v>46149</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45372</v>
+        <v>46160</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44907</v>
+        <v>45642</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44769</v>
+        <v>46128</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4806,14 +4806,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46308</v>
+        <v>45798</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46266</v>
+        <v>46176</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45587</v>
+        <v>46185</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45146</v>
+        <v>46195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44811</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44861</v>
+        <v>45055</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45594</v>
+        <v>44861</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45146</v>
+        <v>45446</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,14 +1287,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45208</v>
+        <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1306,8 +1306,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1350,7 +1355,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1360,14 +1365,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44769</v>
+        <v>45803</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1379,8 +1384,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1423,7 +1433,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1437,10 +1447,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45712</v>
+        <v>44680</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1453,7 +1463,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1496,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1510,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45446</v>
+        <v>45026</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1526,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1569,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2263-2025</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1583,10 +1593,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45673</v>
+        <v>45616</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1599,7 +1609,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1642,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1652,14 +1662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44862</v>
+        <v>45640</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1672,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1715,7 +1725,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 32665-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1725,14 +1735,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45055</v>
+        <v>45838</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1745,7 +1755,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1788,7 +1798,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 45408-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1802,10 +1812,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45673</v>
+        <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1818,7 +1828,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1861,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44838</v>
+        <v>45673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1891,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1934,7 +1944,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 45408-2025</t>
+          <t>A 24453-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1948,10 +1958,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45922</v>
+        <v>45798</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2007,7 +2017,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 2263-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2021,10 +2031,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45527</v>
+        <v>45673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2037,7 +2047,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2080,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2094,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45587</v>
+        <v>45372</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2153,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2167,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45085</v>
+        <v>46149</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2183,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2226,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2240,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45637</v>
+        <v>44907</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2256,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2299,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2313,10 +2323,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44907</v>
+        <v>44769</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2329,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2386,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44680</v>
+        <v>45642</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2402,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2445,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2455,14 +2465,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45640</v>
+        <v>46128</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2475,7 +2485,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2518,7 +2528,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2532,10 +2542,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45026</v>
+        <v>46160</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2548,7 +2558,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2608,7 +2618,7 @@
         <v>45737</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2669,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2683,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46203</v>
+        <v>46176</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2699,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2742,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2756,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45372</v>
+        <v>45587</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2772,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2815,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2829,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46038</v>
+        <v>45146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2845,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2905,7 +2915,7 @@
         <v>46037</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2961,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2975,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46238</v>
+        <v>46038</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2991,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3034,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3044,14 +3054,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45803</v>
+        <v>46185</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3063,13 +3073,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3112,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3126,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45724</v>
+        <v>45085</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3142,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3185,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3199,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45169</v>
+        <v>46195</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3215,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3258,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3268,14 +3273,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45803</v>
+        <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3287,13 +3292,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46092</v>
+        <v>45712</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46099</v>
+        <v>46203</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>45724</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46248</v>
+        <v>46092</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46112</v>
+        <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45222</v>
+        <v>46099</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46248</v>
+        <v>45527</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46136</v>
+        <v>46112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46135</v>
+        <v>46238</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45810</v>
+        <v>46135</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4076,14 +4076,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46308</v>
+        <v>45406</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46266</v>
+        <v>46136</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46136</v>
+        <v>45810</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45406</v>
+        <v>46136</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45616</v>
+        <v>46248</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32665-2025</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45838</v>
+        <v>45169</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46149</v>
+        <v>45594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46160</v>
+        <v>46248</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45642</v>
+        <v>45208</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46128</v>
+        <v>46308</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24453-2025</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45798</v>
+        <v>46266</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46176</v>
+        <v>45222</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4956,10 +4956,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46185</v>
+        <v>44838</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46195</v>
+        <v>45428</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>

--- a/Översikt GRÄSTORP.xlsx
+++ b/Översikt GRÄSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44769</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         <v>44840</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>44806</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>44609</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>44830</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 38064-2022</t>
+          <t>A 49273-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44811</v>
+        <v>44861</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20198-2023</t>
+          <t>A 38064-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45055</v>
+        <v>44811</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 49273-2022</t>
+          <t>A 60189-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1141,14 +1141,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44861</v>
+        <v>45640</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22167-2024</t>
+          <t>A 25554-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45446</v>
+        <v>45803</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1233,8 +1233,13 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1277,7 +1282,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 25554-2025</t>
+          <t>A 25566-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1294,7 +1299,7 @@
         <v>45803</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1312,7 +1317,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1355,7 +1360,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 25566-2025</t>
+          <t>A 35091-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1365,14 +1370,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45803</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1384,13 +1389,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 17666-2022</t>
+          <t>A 2633-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44680</v>
+        <v>46037</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16011-2023</t>
+          <t>A 2756-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45026</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1579,7 +1579,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53943-2024</t>
+          <t>A 40126-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45616</v>
+        <v>45169</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60189-2024</t>
+          <t>A 48865-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1662,14 +1662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45640</v>
+        <v>45594</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>45838</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45922</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 2264-2025</t>
+          <t>A 48596-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45673</v>
+        <v>45208</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>45798</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>45673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11345-2024</t>
+          <t>A 51534-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45372</v>
+        <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21711-2026</t>
+          <t>A 43924-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46149</v>
+        <v>44838</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2236,7 +2236,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59569-2022</t>
+          <t>A 12902-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44907</v>
+        <v>46092</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2309,7 +2309,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 31073-2022</t>
+          <t>A 14103-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44769</v>
+        <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60236-2024</t>
+          <t>A 19282-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45642</v>
+        <v>45428</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18724-2026</t>
+          <t>A 13718-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46128</v>
+        <v>45737</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2482,6 +2482,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>GRÄSTORP</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2528,7 +2533,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 22914-2026</t>
+          <t>A 16496-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2542,10 +2547,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46160</v>
+        <v>46112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2558,7 +2563,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2601,7 +2606,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13718-2025</t>
+          <t>A 20198-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45737</v>
+        <v>45055</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2630,13 +2635,8 @@
           <t>GRÄSTORP</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25293-2026</t>
+          <t>A 22167-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46176</v>
+        <v>45446</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 47573-2024</t>
+          <t>A 19766-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45587</v>
+        <v>46135</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35394-2023</t>
+          <t>A 16172-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45146</v>
+        <v>45406</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 2633-2026</t>
+          <t>A 17666-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46037</v>
+        <v>44680</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 2756-2026</t>
+          <t>A 20041-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46038</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26943-2026</t>
+          <t>A 16011-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46185</v>
+        <v>45026</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24985-2023</t>
+          <t>A 53943-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45085</v>
+        <v>45616</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28065-2026</t>
+          <t>A 26859-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46195</v>
+        <v>45810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59311-2024</t>
+          <t>A 20039-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45637</v>
+        <v>46136</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8650-2025</t>
+          <t>A 21711-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45712</v>
+        <v>46149</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29440-2026</t>
+          <t>A 2264-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46203</v>
+        <v>45673</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3482,7 +3482,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11171-2025</t>
+          <t>A 60236-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45724</v>
+        <v>45642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12902-2026</t>
+          <t>A 18724-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46092</v>
+        <v>46128</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49621-2022</t>
+          <t>A 22914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44862</v>
+        <v>46160</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14103-2026</t>
+          <t>A 11345-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46099</v>
+        <v>45372</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35091-2024</t>
+          <t>A 59569-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45527</v>
+        <v>44907</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16496-2026</t>
+          <t>A 31073-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46112</v>
+        <v>44769</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3920,7 +3920,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 32415-2026</t>
+          <t>A 25293-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46238</v>
+        <v>46176</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19766-2026</t>
+          <t>A 26943-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46135</v>
+        <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16172-2024</t>
+          <t>A 28065-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45406</v>
+        <v>46195</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20041-2026</t>
+          <t>A 47573-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46136</v>
+        <v>45587</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4212,7 +4212,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26859-2025</t>
+          <t>A 35394-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45810</v>
+        <v>45146</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20039-2026</t>
+          <t>A 29440-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46136</v>
+        <v>46203</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33535-2026</t>
+          <t>A 24985-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46248</v>
+        <v>45085</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40126-2023</t>
+          <t>A 59311-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45169</v>
+        <v>45637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48865-2024</t>
+          <t>A 8650-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45594</v>
+        <v>45712</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4577,7 +4577,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 33531-2026</t>
+          <t>A 32415-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48596-2023</t>
+          <t>A 11171-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45208</v>
+        <v>45724</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 42428-2026</t>
+          <t>A 49621-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4733,14 +4733,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46308</v>
+        <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35977-2026</t>
+          <t>A 33535-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46266</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51534-2023</t>
+          <t>A 33531-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45222</v>
+        <v>46248</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -4942,7 +4942,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 43924-2022</t>
+          <t>A 42428-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4952,14 +4952,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44838</v>
+        <v>46308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19282-2024</t>
+          <t>A 35977-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45428</v>
+        <v>46266</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>44690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
